--- a/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -653,160 +653,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1530500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1281800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>910900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>562700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2068300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2050900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1851600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1712500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1923800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2050200</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>882400</v>
+      </c>
+      <c r="E9" s="3">
         <v>816300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>537700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>309400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1250300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1266100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1145100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1086100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1258600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1304000</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>648100</v>
+      </c>
+      <c r="E10" s="3">
         <v>465500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>373200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>253300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>818000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>784800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>706500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>626400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>665200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>746200</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,41 +832,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E12" s="3">
         <v>18400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>40500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>35800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>37200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38800</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -885,75 +901,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E14" s="3">
         <v>15400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>24100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>137200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>33900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>34900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12900</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E15" s="3">
         <v>34000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>23500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>34000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>57400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>55100</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -964,74 +989,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1340000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1174700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>824300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>481700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1733000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1741000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1597100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1517100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1749500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1846500</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>190500</v>
+      </c>
+      <c r="E18" s="3">
         <v>107100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>86600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>81000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>335300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>309900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>254500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>195400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>174300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>203700</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1045,173 +1077,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E20" s="3">
         <v>3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-40400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7200</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E21" s="3">
         <v>165200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>164600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>145800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>381500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>400200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>346900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>301000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>292800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>308700</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E22" s="3">
         <v>26900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>58600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>69100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>70100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>88300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>91400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>87900</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>146800</v>
+      </c>
+      <c r="E23" s="3">
         <v>83800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>52400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>236300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>238800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>187100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>107300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>86000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>108600</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E24" s="3">
         <v>26800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>54100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>52700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>47400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16800</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1242,75 +1290,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E26" s="3">
         <v>57000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>49700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>182200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>186100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>139700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>68900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>91800</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E27" s="3">
         <v>57000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>50000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>167500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>166500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>116400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>84400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>69300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>91800</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1341,42 +1398,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E29" s="3">
         <v>4700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>70900</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>83000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-155400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-63700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-17600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-1400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-8000</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1407,9 +1470,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1440,75 +1506,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>40400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7200</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E33" s="3">
         <v>61700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>120900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>117800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>165700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>52700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>66800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>67900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>83800</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1539,80 +1614,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E35" s="3">
         <v>61700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>120900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>117800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>165700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>52700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>66800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>67900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>83800</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1626,8 +1710,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1641,41 +1726,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E41" s="3">
         <v>124800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>96600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>255600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>573400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>292500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>193200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>490100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>484600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>370300</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1706,141 +1795,156 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>227200</v>
+      </c>
+      <c r="E43" s="3">
         <v>238000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>177200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>284600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>334700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>337600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>332200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>322900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>317600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>672000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E44" s="3">
         <v>366700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>184500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>330100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>317500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>316500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>304100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>314900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>327200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>367700</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E45" s="3">
         <v>28000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>211200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>50200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>46700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56200</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>667800</v>
+      </c>
+      <c r="E46" s="3">
         <v>757500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>474800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>907700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1264300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>982900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>997700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1178100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1176100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1127600</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -1869,77 +1973,86 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>27600</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>226700</v>
+      </c>
+      <c r="E48" s="3">
         <v>226400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>78500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>506100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>449900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>383000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>852900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>400900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>397200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>835200</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1748400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1786700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>433200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1894700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1836100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1811200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1807000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1876800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1714700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1790000</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1970,9 +2083,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2003,42 +2119,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E52" s="3">
         <v>93400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>91200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>92600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>76800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>82600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>338500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>83500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>66800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>84000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2069,42 +2191,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2667000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2864000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1077700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3401100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3627100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3259700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3423700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3539300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3354800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3409300</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2118,8 +2246,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2133,206 +2262,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E57" s="3">
         <v>116900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>105100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>129400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>185600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>191700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>189900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>197800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>234100</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>5700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>76400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24300</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E59" s="3">
         <v>166700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>129700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>185700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>193500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>204100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>246000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>186000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>183400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>187500</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E60" s="3">
         <v>289300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>240400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>317500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>455500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>397000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>454200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>400300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>404400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>433000</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>494400</v>
+      </c>
+      <c r="E61" s="3">
         <v>530200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>533900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1189200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1397000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1236800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1352100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1606200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1899900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1915700</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>348900</v>
+      </c>
+      <c r="E62" s="3">
         <v>429500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>177000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>455100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>460900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>394900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>469600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>462200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>462500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>507900</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2363,9 +2511,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2396,9 +2547,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2429,42 +2583,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1064200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1249000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>951300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1964800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2316100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2031100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2211000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2468700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2766200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2856400</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2478,8 +2638,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2510,9 +2671,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2543,9 +2707,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2576,9 +2743,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2609,42 +2779,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-1178200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1164900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1236900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>116000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>85900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-55500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-129600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-197500</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2675,9 +2851,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2708,9 +2887,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2741,42 +2923,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1602800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1615000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>126400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1436300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1311000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1228600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1212700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1070600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>588600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>552900</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2807,80 +2995,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E81" s="3">
         <v>61700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>120900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>117800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>165700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>52700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>66800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>67900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>83800</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2894,41 +3091,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E83" s="3">
         <v>54500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>67000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>86600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>92300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>89700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>105400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>115400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>112200</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2959,9 +3160,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2992,9 +3196,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3025,9 +3232,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3058,9 +3268,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3091,42 +3304,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E89" s="3">
         <v>97000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>223600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>196300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>298600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>258100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>228500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>195100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>219000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>245900</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3140,41 +3359,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-52100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-48800</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3205,9 +3428,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3238,42 +3464,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-122500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-123100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-53300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-208800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-264000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-177300</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3287,41 +3519,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-32500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-36400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-28800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-27200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-23200</v>
       </c>
       <c r="I96" s="3">
         <v>-23200</v>
       </c>
       <c r="J96" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-4400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3352,9 +3588,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3385,9 +3624,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3418,106 +3660,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-239200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-61100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-356200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-409600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>114900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-116700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-308800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>79900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-56300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17400</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>18000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>16600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-19900</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E102" s="3">
         <v>28200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-159000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-317800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>280900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>74900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-272500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>114300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>31300</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>ZWS</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -724,10 +727,10 @@
         <v>910900</v>
       </c>
       <c r="G8" s="3">
-        <v>562700</v>
+        <v>1109700</v>
       </c>
       <c r="H8" s="3">
-        <v>2068300</v>
+        <v>710100</v>
       </c>
       <c r="I8" s="3">
         <v>2050900</v>
@@ -760,16 +763,16 @@
         <v>537700</v>
       </c>
       <c r="G9" s="3">
-        <v>309400</v>
+        <v>639300</v>
       </c>
       <c r="H9" s="3">
-        <v>1250300</v>
+        <v>387500</v>
       </c>
       <c r="I9" s="3">
-        <v>1266100</v>
+        <v>1262200</v>
       </c>
       <c r="J9" s="3">
-        <v>1145100</v>
+        <v>1142800</v>
       </c>
       <c r="K9" s="3">
         <v>1086100</v>
@@ -796,16 +799,16 @@
         <v>373200</v>
       </c>
       <c r="G10" s="3">
-        <v>253300</v>
+        <v>470400</v>
       </c>
       <c r="H10" s="3">
-        <v>818000</v>
+        <v>322600</v>
       </c>
       <c r="I10" s="3">
-        <v>784800</v>
+        <v>788700</v>
       </c>
       <c r="J10" s="3">
-        <v>706500</v>
+        <v>708800</v>
       </c>
       <c r="K10" s="3">
         <v>626400</v>
@@ -851,7 +854,7 @@
         <v>9600</v>
       </c>
       <c r="H12" s="3">
-        <v>40500</v>
+        <v>13200</v>
       </c>
       <c r="I12" s="3">
         <v>41700</v>
@@ -914,22 +917,22 @@
         <v>27600</v>
       </c>
       <c r="E14" s="3">
-        <v>15400</v>
+        <v>49100</v>
       </c>
       <c r="F14" s="3">
         <v>24100</v>
       </c>
       <c r="G14" s="3">
-        <v>3600</v>
+        <v>1700</v>
       </c>
       <c r="H14" s="3">
-        <v>14500</v>
+        <v>3200</v>
       </c>
       <c r="I14" s="3">
-        <v>7800</v>
+        <v>11700</v>
       </c>
       <c r="J14" s="3">
-        <v>137200</v>
+        <v>28300</v>
       </c>
       <c r="K14" s="3">
         <v>33900</v>
@@ -947,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>60400</v>
+        <v>58700</v>
       </c>
       <c r="E15" s="3">
         <v>34000</v>
@@ -956,10 +959,10 @@
         <v>23500</v>
       </c>
       <c r="G15" s="3">
-        <v>16900</v>
+        <v>26000</v>
       </c>
       <c r="H15" s="3">
-        <v>35400</v>
+        <v>20900</v>
       </c>
       <c r="I15" s="3">
         <v>34000</v>
@@ -996,25 +999,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1340000</v>
+        <v>1315600</v>
       </c>
       <c r="E17" s="3">
-        <v>1174700</v>
+        <v>1123100</v>
       </c>
       <c r="F17" s="3">
-        <v>824300</v>
+        <v>795100</v>
       </c>
       <c r="G17" s="3">
-        <v>481700</v>
+        <v>968100</v>
       </c>
       <c r="H17" s="3">
-        <v>1733000</v>
+        <v>625500</v>
       </c>
       <c r="I17" s="3">
-        <v>1741000</v>
+        <v>1727000</v>
       </c>
       <c r="J17" s="3">
-        <v>1597100</v>
+        <v>1562200</v>
       </c>
       <c r="K17" s="3">
         <v>1517100</v>
@@ -1032,25 +1035,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>190500</v>
+        <v>214900</v>
       </c>
       <c r="E18" s="3">
-        <v>107100</v>
+        <v>158700</v>
       </c>
       <c r="F18" s="3">
-        <v>86600</v>
+        <v>115800</v>
       </c>
       <c r="G18" s="3">
-        <v>81000</v>
+        <v>141600</v>
       </c>
       <c r="H18" s="3">
-        <v>335300</v>
+        <v>84600</v>
       </c>
       <c r="I18" s="3">
-        <v>309900</v>
+        <v>323900</v>
       </c>
       <c r="J18" s="3">
-        <v>254500</v>
+        <v>289400</v>
       </c>
       <c r="K18" s="3">
         <v>195400</v>
@@ -1084,25 +1087,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-5200</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="3">
-        <v>3600</v>
+        <v>-1100</v>
       </c>
       <c r="F20" s="3">
-        <v>500</v>
+        <v>4600</v>
       </c>
       <c r="G20" s="3">
-        <v>-2200</v>
+        <v>1700</v>
       </c>
       <c r="H20" s="3">
-        <v>-40400</v>
+        <v>1400</v>
       </c>
       <c r="I20" s="3">
-        <v>-2000</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>2700</v>
+        <v>-1100</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1120,25 +1123,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>273200</v>
+        <v>271600</v>
       </c>
       <c r="E21" s="3">
-        <v>165200</v>
+        <v>193800</v>
       </c>
       <c r="F21" s="3">
-        <v>164600</v>
+        <v>134700</v>
       </c>
       <c r="G21" s="3">
-        <v>145800</v>
+        <v>165900</v>
       </c>
       <c r="H21" s="3">
-        <v>381500</v>
+        <v>104100</v>
       </c>
       <c r="I21" s="3">
-        <v>400200</v>
+        <v>358000</v>
       </c>
       <c r="J21" s="3">
-        <v>346900</v>
+        <v>322700</v>
       </c>
       <c r="K21" s="3">
         <v>301000</v>
@@ -1168,13 +1171,13 @@
         <v>33300</v>
       </c>
       <c r="H22" s="3">
-        <v>58600</v>
+        <v>56600</v>
       </c>
       <c r="I22" s="3">
-        <v>69100</v>
+        <v>69900</v>
       </c>
       <c r="J22" s="3">
-        <v>70100</v>
+        <v>75100</v>
       </c>
       <c r="K22" s="3">
         <v>88300</v>
@@ -1201,13 +1204,13 @@
         <v>52400</v>
       </c>
       <c r="G23" s="3">
-        <v>45500</v>
+        <v>80500</v>
       </c>
       <c r="H23" s="3">
-        <v>236300</v>
+        <v>23400</v>
       </c>
       <c r="I23" s="3">
-        <v>238800</v>
+        <v>242400</v>
       </c>
       <c r="J23" s="3">
         <v>187100</v>
@@ -1237,16 +1240,16 @@
         <v>2700</v>
       </c>
       <c r="G24" s="3">
-        <v>10500</v>
+        <v>16900</v>
       </c>
       <c r="H24" s="3">
-        <v>54100</v>
+        <v>4400</v>
       </c>
       <c r="I24" s="3">
-        <v>52700</v>
+        <v>53400</v>
       </c>
       <c r="J24" s="3">
-        <v>47400</v>
+        <v>-19500</v>
       </c>
       <c r="K24" s="3">
         <v>15600</v>
@@ -1309,16 +1312,16 @@
         <v>49700</v>
       </c>
       <c r="G26" s="3">
-        <v>35000</v>
+        <v>63600</v>
       </c>
       <c r="H26" s="3">
-        <v>182200</v>
+        <v>19000</v>
       </c>
       <c r="I26" s="3">
-        <v>186100</v>
+        <v>189000</v>
       </c>
       <c r="J26" s="3">
-        <v>139700</v>
+        <v>206600</v>
       </c>
       <c r="K26" s="3">
         <v>91700</v>
@@ -1336,25 +1339,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>104200</v>
+        <v>112700</v>
       </c>
       <c r="E27" s="3">
-        <v>57000</v>
+        <v>61700</v>
       </c>
       <c r="F27" s="3">
-        <v>50000</v>
+        <v>120900</v>
       </c>
       <c r="G27" s="3">
-        <v>34800</v>
+        <v>146700</v>
       </c>
       <c r="H27" s="3">
-        <v>167500</v>
+        <v>165700</v>
       </c>
       <c r="I27" s="3">
-        <v>166500</v>
+        <v>11100</v>
       </c>
       <c r="J27" s="3">
-        <v>116400</v>
+        <v>52700</v>
       </c>
       <c r="K27" s="3">
         <v>84400</v>
@@ -1414,19 +1417,19 @@
         <v>4700</v>
       </c>
       <c r="F29" s="3">
-        <v>70900</v>
+        <v>71200</v>
       </c>
       <c r="G29" s="3">
-        <v>83000</v>
+        <v>83200</v>
       </c>
       <c r="H29" s="3">
-        <v>-1800</v>
+        <v>161100</v>
       </c>
       <c r="I29" s="3">
-        <v>-155400</v>
+        <v>-154700</v>
       </c>
       <c r="J29" s="3">
-        <v>-63700</v>
+        <v>-130600</v>
       </c>
       <c r="K29" s="3">
         <v>-17600</v>
@@ -1516,25 +1519,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>5200</v>
+        <v>-2000</v>
       </c>
       <c r="E32" s="3">
-        <v>-3600</v>
+        <v>1100</v>
       </c>
       <c r="F32" s="3">
-        <v>-500</v>
+        <v>-4600</v>
       </c>
       <c r="G32" s="3">
-        <v>2200</v>
+        <v>-1700</v>
       </c>
       <c r="H32" s="3">
-        <v>40400</v>
+        <v>-1400</v>
       </c>
       <c r="I32" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>-2700</v>
+        <v>1100</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
@@ -1561,16 +1564,16 @@
         <v>120900</v>
       </c>
       <c r="G33" s="3">
-        <v>117800</v>
+        <v>146700</v>
       </c>
       <c r="H33" s="3">
-        <v>165700</v>
+        <v>180100</v>
       </c>
       <c r="I33" s="3">
-        <v>11100</v>
+        <v>34300</v>
       </c>
       <c r="J33" s="3">
-        <v>52700</v>
+        <v>75900</v>
       </c>
       <c r="K33" s="3">
         <v>66800</v>
@@ -1633,16 +1636,16 @@
         <v>120900</v>
       </c>
       <c r="G35" s="3">
-        <v>117800</v>
+        <v>146700</v>
       </c>
       <c r="H35" s="3">
-        <v>165700</v>
+        <v>180100</v>
       </c>
       <c r="I35" s="3">
-        <v>11100</v>
+        <v>34300</v>
       </c>
       <c r="J35" s="3">
-        <v>52700</v>
+        <v>75900</v>
       </c>
       <c r="K35" s="3">
         <v>66800</v>
@@ -1742,7 +1745,7 @@
         <v>96600</v>
       </c>
       <c r="G41" s="3">
-        <v>255600</v>
+        <v>62300</v>
       </c>
       <c r="H41" s="3">
         <v>573400</v>
@@ -1814,10 +1817,10 @@
         <v>177200</v>
       </c>
       <c r="G43" s="3">
-        <v>284600</v>
+        <v>112100</v>
       </c>
       <c r="H43" s="3">
-        <v>334700</v>
+        <v>338100</v>
       </c>
       <c r="I43" s="3">
         <v>337600</v>
@@ -1850,7 +1853,7 @@
         <v>184500</v>
       </c>
       <c r="G44" s="3">
-        <v>330100</v>
+        <v>136100</v>
       </c>
       <c r="H44" s="3">
         <v>317500</v>
@@ -1886,16 +1889,16 @@
         <v>16500</v>
       </c>
       <c r="G45" s="3">
-        <v>37400</v>
+        <v>597200</v>
       </c>
       <c r="H45" s="3">
-        <v>38700</v>
+        <v>35300</v>
       </c>
       <c r="I45" s="3">
         <v>36300</v>
       </c>
       <c r="J45" s="3">
-        <v>211200</v>
+        <v>168200</v>
       </c>
       <c r="K45" s="3">
         <v>50200</v>
@@ -1948,26 +1951,26 @@
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1994,7 +1997,7 @@
         <v>78500</v>
       </c>
       <c r="G48" s="3">
-        <v>506100</v>
+        <v>87700</v>
       </c>
       <c r="H48" s="3">
         <v>449900</v>
@@ -2003,7 +2006,7 @@
         <v>383000</v>
       </c>
       <c r="J48" s="3">
-        <v>852900</v>
+        <v>396500</v>
       </c>
       <c r="K48" s="3">
         <v>400900</v>
@@ -2030,7 +2033,7 @@
         <v>433200</v>
       </c>
       <c r="G49" s="3">
-        <v>1894700</v>
+        <v>445100</v>
       </c>
       <c r="H49" s="3">
         <v>1836100</v>
@@ -2129,25 +2132,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>24100</v>
+        <v>20800</v>
       </c>
       <c r="E52" s="3">
-        <v>93400</v>
+        <v>90300</v>
       </c>
       <c r="F52" s="3">
-        <v>91200</v>
+        <v>86800</v>
       </c>
       <c r="G52" s="3">
-        <v>92600</v>
+        <v>1954800</v>
       </c>
       <c r="H52" s="3">
-        <v>76800</v>
+        <v>63200</v>
       </c>
       <c r="I52" s="3">
-        <v>82600</v>
+        <v>67900</v>
       </c>
       <c r="J52" s="3">
-        <v>338500</v>
+        <v>209100</v>
       </c>
       <c r="K52" s="3">
         <v>83500</v>
@@ -2278,7 +2281,7 @@
         <v>105100</v>
       </c>
       <c r="G57" s="3">
-        <v>129400</v>
+        <v>41300</v>
       </c>
       <c r="H57" s="3">
         <v>185600</v>
@@ -2305,25 +2308,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>900</v>
+        <v>11500</v>
       </c>
       <c r="E58" s="3">
-        <v>5700</v>
+        <v>15100</v>
       </c>
       <c r="F58" s="3">
-        <v>5600</v>
+        <v>11700</v>
       </c>
       <c r="G58" s="3">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="H58" s="3">
-        <v>76400</v>
+        <v>89200</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
       </c>
       <c r="J58" s="3">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="K58" s="3">
         <v>16500</v>
@@ -2341,25 +2344,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>163600</v>
+        <v>23700</v>
       </c>
       <c r="E59" s="3">
-        <v>166700</v>
+        <v>47700</v>
       </c>
       <c r="F59" s="3">
-        <v>129700</v>
+        <v>29900</v>
       </c>
       <c r="G59" s="3">
-        <v>185700</v>
+        <v>220500</v>
       </c>
       <c r="H59" s="3">
-        <v>193500</v>
+        <v>56600</v>
       </c>
       <c r="I59" s="3">
-        <v>204100</v>
+        <v>79500</v>
       </c>
       <c r="J59" s="3">
-        <v>246000</v>
+        <v>142100</v>
       </c>
       <c r="K59" s="3">
         <v>186000</v>
@@ -2413,25 +2416,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>494400</v>
+        <v>531700</v>
       </c>
       <c r="E61" s="3">
-        <v>530200</v>
+        <v>564400</v>
       </c>
       <c r="F61" s="3">
-        <v>533900</v>
+        <v>542800</v>
       </c>
       <c r="G61" s="3">
-        <v>1189200</v>
+        <v>1131400</v>
       </c>
       <c r="H61" s="3">
-        <v>1397000</v>
+        <v>1460100</v>
       </c>
       <c r="I61" s="3">
         <v>1236800</v>
       </c>
       <c r="J61" s="3">
-        <v>1352100</v>
+        <v>1359600</v>
       </c>
       <c r="K61" s="3">
         <v>1606200</v>
@@ -2449,25 +2452,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>348900</v>
+        <v>65000</v>
       </c>
       <c r="E62" s="3">
-        <v>429500</v>
+        <v>123400</v>
       </c>
       <c r="F62" s="3">
-        <v>177000</v>
+        <v>107700</v>
       </c>
       <c r="G62" s="3">
-        <v>455100</v>
+        <v>424500</v>
       </c>
       <c r="H62" s="3">
-        <v>460900</v>
+        <v>87200</v>
       </c>
       <c r="I62" s="3">
-        <v>394900</v>
+        <v>111000</v>
       </c>
       <c r="J62" s="3">
-        <v>469600</v>
+        <v>84600</v>
       </c>
       <c r="K62" s="3">
         <v>462200</v>
@@ -2602,16 +2605,16 @@
         <v>951300</v>
       </c>
       <c r="G66" s="3">
-        <v>1964800</v>
+        <v>1961800</v>
       </c>
       <c r="H66" s="3">
-        <v>2316100</v>
+        <v>2313400</v>
       </c>
       <c r="I66" s="3">
-        <v>2031100</v>
+        <v>2028700</v>
       </c>
       <c r="J66" s="3">
-        <v>2211000</v>
+        <v>2210900</v>
       </c>
       <c r="K66" s="3">
         <v>2468700</v>
@@ -3055,16 +3058,16 @@
         <v>120900</v>
       </c>
       <c r="G81" s="3">
-        <v>117800</v>
+        <v>146700</v>
       </c>
       <c r="H81" s="3">
-        <v>165700</v>
+        <v>180100</v>
       </c>
       <c r="I81" s="3">
-        <v>11100</v>
+        <v>34300</v>
       </c>
       <c r="J81" s="3">
-        <v>52700</v>
+        <v>75900</v>
       </c>
       <c r="K81" s="3">
         <v>66800</v>
@@ -3098,25 +3101,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>87900</v>
+        <v>29200</v>
       </c>
       <c r="E83" s="3">
-        <v>54500</v>
+        <v>20500</v>
       </c>
       <c r="F83" s="3">
-        <v>77500</v>
+        <v>44100</v>
       </c>
       <c r="G83" s="3">
-        <v>67000</v>
+        <v>52600</v>
       </c>
       <c r="H83" s="3">
-        <v>86600</v>
+        <v>51200</v>
       </c>
       <c r="I83" s="3">
-        <v>92300</v>
+        <v>54100</v>
       </c>
       <c r="J83" s="3">
-        <v>89700</v>
+        <v>53800</v>
       </c>
       <c r="K83" s="3">
         <v>105400</v>
@@ -3323,7 +3326,7 @@
         <v>223600</v>
       </c>
       <c r="G89" s="3">
-        <v>196300</v>
+        <v>320200</v>
       </c>
       <c r="H89" s="3">
         <v>298600</v>
@@ -3526,25 +3529,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-50400</v>
+        <v>50400</v>
       </c>
       <c r="E96" s="3">
-        <v>-32500</v>
+        <v>32500</v>
       </c>
       <c r="F96" s="3">
-        <v>-36400</v>
+        <v>36400</v>
       </c>
       <c r="G96" s="3">
-        <v>-28800</v>
+        <v>28800</v>
       </c>
       <c r="H96" s="3">
-        <v>-27200</v>
+        <v>9800</v>
       </c>
       <c r="I96" s="3">
-        <v>-23200</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-23200</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-4400</v>
@@ -3679,7 +3682,7 @@
         <v>-356200</v>
       </c>
       <c r="G100" s="3">
-        <v>-409600</v>
+        <v>-156200</v>
       </c>
       <c r="H100" s="3">
         <v>114900</v>
@@ -3751,7 +3754,7 @@
         <v>-159000</v>
       </c>
       <c r="G102" s="3">
-        <v>-317800</v>
+        <v>59500</v>
       </c>
       <c r="H102" s="3">
         <v>280900</v>

--- a/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>ZWS</t>
   </si>
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1566500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1530500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1281800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>910900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1109700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>710100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2050900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1851600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1712500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1923800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2050200</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>859500</v>
+      </c>
+      <c r="E9" s="3">
         <v>882400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>816300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>537700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>639300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>387500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1262200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1142800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1086100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1258600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1304000</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>707000</v>
+      </c>
+      <c r="E10" s="3">
         <v>648100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>465500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>373200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>470400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>322600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>788700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>708800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>626400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>665200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>746200</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E12" s="3">
         <v>23700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>41700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>37200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38800</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,81 +923,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E14" s="3">
         <v>27600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>49100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>28300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>33900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>34900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12900</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E15" s="3">
         <v>58700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>34000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>57400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55100</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1311100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1315600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1123100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>795100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>968100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>625500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1727000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1562200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1517100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1749500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1846500</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>255400</v>
+      </c>
+      <c r="E18" s="3">
         <v>214900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>158700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>115800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>141600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>84600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>323900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>289400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>195400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>174300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>203700</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1081,188 +1113,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7200</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>312700</v>
+      </c>
+      <c r="E21" s="3">
         <v>271600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>193800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>134700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>165900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>104100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>358000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>322700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>301000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>292800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>308700</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E22" s="3">
         <v>38500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>26900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>56600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>69900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>75100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>88300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>91400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>87900</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E23" s="3">
         <v>146800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>83800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>52400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>80500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>242400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>187100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>107300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>86000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>108600</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E24" s="3">
         <v>42600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>53400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-19500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16800</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>158900</v>
+      </c>
+      <c r="E26" s="3">
         <v>104200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>57000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>49700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>63600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>189000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>206600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>91700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>68900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>91800</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E27" s="3">
         <v>112700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>61700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>120900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>146700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>165700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>52700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>84400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>69300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>91800</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1404,45 +1461,51 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E29" s="3">
         <v>8500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>4700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>71200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>83200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>161100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-154700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-130600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-17600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-8000</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7200</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E33" s="3">
         <v>112700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>61700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>120900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>146700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>180100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>75900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>66800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>67900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>83800</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E35" s="3">
         <v>112700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>61700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>120900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>146700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>180100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>75900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>66800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>67900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>83800</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1730,44 +1815,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E41" s="3">
         <v>136700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>124800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>96600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>62300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>573400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>292500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>490100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>484600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>370300</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1801,153 +1890,168 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>221800</v>
+      </c>
+      <c r="E43" s="3">
         <v>227200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>238000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>177200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>112100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>338100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>337600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>332200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>322900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>317600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>672000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>272600</v>
+      </c>
+      <c r="E44" s="3">
         <v>277600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>366700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>184500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>136100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>317500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>316500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>304100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>314900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>327200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>367700</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E45" s="3">
         <v>26300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>597200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>168200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>50200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>46700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56200</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>722100</v>
+      </c>
+      <c r="E46" s="3">
         <v>667800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>757500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>474800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>907700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1264300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>982900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>997700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1178100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1176100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1127600</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -1972,90 +2076,99 @@
       <c r="J47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>27600</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>215200</v>
+      </c>
+      <c r="E48" s="3">
         <v>226700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>226400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>87700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>449900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>383000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>396500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>400900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>397200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>835200</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1685800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1748400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1786700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>433200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>445100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1836100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1811200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1807000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1876800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1714700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1790000</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2125,45 +2241,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E52" s="3">
         <v>20800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>90300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>86800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1954800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>67900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>209100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>66800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>84000</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2648500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2667000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2864000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1077700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3401100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3627100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3259700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3423700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3539300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3354800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3409300</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2266,224 +2395,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E57" s="3">
         <v>56400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>116900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>105100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>185600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>191700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>189900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>197800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>234100</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E58" s="3">
         <v>11500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>89200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24300</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E59" s="3">
         <v>23700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>220500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>79500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>142100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>186000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>183400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>187500</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>247800</v>
+      </c>
+      <c r="E60" s="3">
         <v>220900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>289300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>240400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>317500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>455500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>397000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>454200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>400300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>404400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>433000</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>538100</v>
+      </c>
+      <c r="E61" s="3">
         <v>531700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>564400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>542800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1131400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1460100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1236800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1359600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1606200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1899900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1915700</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E62" s="3">
         <v>65000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>123400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>107700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>424500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>87200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>111000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>84600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>462200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>462500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>507900</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2589,45 +2743,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1061700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1064200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1249000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>951300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1961800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2313400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2028700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2210900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2468700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2766200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2856400</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-1168700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1178200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1164900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1236900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>116000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>85900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-55500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-129600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-197500</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1586800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1602800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1615000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>126400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1436300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1311000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1228600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1212700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1070600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>588600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>552900</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E81" s="3">
         <v>112700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>61700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>120900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>146700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>180100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>75900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>66800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>67900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>83800</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3095,8 +3292,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -3104,35 +3302,38 @@
         <v>29200</v>
       </c>
       <c r="E83" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F83" s="3">
         <v>20500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>44100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>51200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>53800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>105400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>115400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>112200</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>293500</v>
+      </c>
+      <c r="E89" s="3">
         <v>253900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>97000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>223600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>320200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>298600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>258100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>228500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>195100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>219000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>245900</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-52100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-48800</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-122500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-123100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-53300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-208800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-264000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-177300</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3523,44 +3755,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E96" s="3">
         <v>50400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>32500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>36400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>28800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>9800</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-4400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3666,115 +3908,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-207500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-239200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-61100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-356200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-156200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>114900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-116700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-308800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>79900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-56300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17400</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E101" s="3">
         <v>1800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>18000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>16600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-19900</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E102" s="3">
         <v>11900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-159000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>59500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>280900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>74900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-272500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>114300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>31300</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZWS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>ZWS</t>
   </si>
@@ -656,184 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1695900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1566500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1530500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1281800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>910900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1109700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>710100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2050900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1851600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1712500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1923800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2050200</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>931100</v>
+      </c>
+      <c r="E9" s="3">
         <v>859500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>882400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>816300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>537700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>639300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>387500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1262200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1142800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1086100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1258600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1304000</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>764800</v>
+      </c>
+      <c r="E10" s="3">
         <v>707000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>648100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>465500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>373200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>470400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>322600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>788700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>708800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>626400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>665200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>746200</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -849,47 +861,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E12" s="3">
         <v>25900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>41700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>37200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>38800</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -926,87 +942,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>13500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>49100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>24100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>28300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>33900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>34900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12900</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E15" s="3">
         <v>59100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>58700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>23500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>57400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55100</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,86 +1044,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1409300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1311100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1315600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1123100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>795100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>968100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>625500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1727000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1562200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1517100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1749500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1846500</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>286600</v>
+      </c>
+      <c r="E18" s="3">
         <v>255400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>214900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>158700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>115800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>141600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>84600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>323900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>289400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>195400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>174300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>203700</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1114,203 +1146,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7200</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>342500</v>
+      </c>
+      <c r="E21" s="3">
         <v>312700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>271600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>193800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>134700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>165900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>104100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>358000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>322700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>301000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>292800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>308700</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E22" s="3">
         <v>33100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>38500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>56600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>69900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>75100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>88300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>91400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>87900</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>256300</v>
+      </c>
+      <c r="E23" s="3">
         <v>207000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>146800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>83800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>52400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>80500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>242400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>187100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>107300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>86000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>108600</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E24" s="3">
         <v>48100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>42600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>53400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-19500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16800</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,87 +1395,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>192400</v>
+      </c>
+      <c r="E26" s="3">
         <v>158900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>104200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>57000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>49700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>63600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>189000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>206600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>91700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>68900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>91800</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E27" s="3">
         <v>160200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>61700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>120900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>146700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>165700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>52700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>84400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>69300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>91800</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1464,48 +1521,54 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E29" s="3">
         <v>1300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>8500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>4700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>71200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>83200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>161100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-154700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-130600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-17600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-8000</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1581,87 +1647,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7200</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E33" s="3">
         <v>160200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>112700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>61700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>120900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>146700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>180100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>75900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>66800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>67900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>83800</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1698,92 +1773,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E35" s="3">
         <v>160200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>112700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>61700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>120900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>146700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>180100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>75900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>66800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>67900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>83800</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1816,47 +1901,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E41" s="3">
         <v>198000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>124800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>96600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>62300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>573400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>292500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>193200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>490100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>484600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>370300</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1893,165 +1982,180 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>198100</v>
+      </c>
+      <c r="E43" s="3">
         <v>221800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>227200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>238000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>177200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>112100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>338100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>337600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>332200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>322900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>317600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>672000</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>274400</v>
+      </c>
+      <c r="E44" s="3">
         <v>272600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>277600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>366700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>184500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>136100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>317500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>316500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>304100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>314900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>327200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>367700</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E45" s="3">
         <v>29700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>597200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>168200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>46700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56200</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>811700</v>
+      </c>
+      <c r="E46" s="3">
         <v>722100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>667800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>757500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>474800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>907700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1264300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>982900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>997700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1178100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1176100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1127600</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2079,96 +2183,105 @@
       <c r="K47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>27600</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E48" s="3">
         <v>215200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>226700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>226400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>78500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>87700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>449900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>383000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>396500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>400900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>397200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>835200</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1630000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1685800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1748400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1786700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>433200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>445100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1836100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1811200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1807000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1876800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1714700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1790000</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2244,48 +2360,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E52" s="3">
         <v>22500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>90300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>86800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1954800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>67900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>209100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>83500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>66800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>84000</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2322,48 +2444,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2679400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2648500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2667000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2864000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1077700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3401100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3627100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3259700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3423700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3539300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3354800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3409300</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2396,242 +2525,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E57" s="3">
         <v>71700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>116900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>105100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>185600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>191700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>189900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>197800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>234100</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E58" s="3">
         <v>13500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>89200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24300</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E59" s="3">
         <v>24400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>220500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>56600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>79500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>142100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>186000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>183400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>187500</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>259400</v>
+      </c>
+      <c r="E60" s="3">
         <v>247800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>220900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>289300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>240400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>317500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>455500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>397000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>454200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>400300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>404400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>433000</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>537600</v>
+      </c>
+      <c r="E61" s="3">
         <v>538100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>531700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>564400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>542800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1131400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1460100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1236800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1359600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1606200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1899900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1915700</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E62" s="3">
         <v>65200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>65000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>123400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>107700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>424500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>87200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>111000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>84600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>462200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>462500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>507900</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2746,48 +2900,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1076100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1061700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1064200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1249000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>951300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1961800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2313400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2028700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2210900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2468700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2766200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2856400</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2958,48 +3128,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-1131700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1168700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1178200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1164900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1236900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>116000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>85900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-55500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-129600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-197500</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3114,48 +3296,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1603300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1586800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1602800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1615000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>126400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1436300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1311000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1228600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1212700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1070600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>588600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>552900</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3192,92 +3380,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E81" s="3">
         <v>160200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>112700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>61700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>120900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>146700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>180100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>75900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>66800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>67900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>83800</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3293,47 +3490,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>29200</v>
+        <v>30000</v>
       </c>
       <c r="E83" s="3">
         <v>29200</v>
       </c>
       <c r="F83" s="3">
+        <v>29200</v>
+      </c>
+      <c r="G83" s="3">
         <v>20500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>51200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>54100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>53800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>105400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>115400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>112200</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3526,48 +3739,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>346500</v>
+      </c>
+      <c r="E89" s="3">
         <v>293500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>253900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>97000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>223600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>320200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>298600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>258100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>228500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>195100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>219000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>245900</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3583,47 +3802,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-52100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-48800</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3699,48 +3925,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-122500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-123100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-53300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-208800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-264000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-177300</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3756,47 +3988,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E96" s="3">
         <v>56600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>50400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>32500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>36400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>28800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>9800</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-4400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3911,124 +4153,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-217300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-207500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-239200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-61100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-356200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-156200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>114900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-116700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-308800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>79900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-56300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17400</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>18000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>16600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-19900</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E102" s="3">
         <v>61300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-159000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>59500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>280900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>74900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-272500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>114300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31300</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
